--- a/naver_webtoon_one_title_final_v4/한계 찢는 천재마법사_회차정보.xlsx
+++ b/naver_webtoon_one_title_final_v4/한계 찢는 천재마법사_회차정보.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,10 +566,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>3202</v>
+        <v>3277</v>
       </c>
       <c r="L2" t="n">
-        <v>3402</v>
+        <v>3506</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -578,12 +578,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:47.082963</t>
+          <t>2026-06-27 01:41:32.930381</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -649,10 +649,10 @@
         <v>9.67</v>
       </c>
       <c r="K3" t="n">
-        <v>3099</v>
+        <v>3184</v>
       </c>
       <c r="L3" t="n">
-        <v>3192</v>
+        <v>3290</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -661,12 +661,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:54.464240</t>
+          <t>2026-06-27 01:41:41.895311</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -732,10 +732,10 @@
         <v>9.43</v>
       </c>
       <c r="K4" t="n">
-        <v>2553</v>
+        <v>2620</v>
       </c>
       <c r="L4" t="n">
-        <v>2769</v>
+        <v>2856</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -744,12 +744,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:59.934830</t>
+          <t>2026-06-27 01:41:48.593761</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="K5" t="n">
-        <v>2220</v>
+        <v>2283</v>
       </c>
       <c r="L5" t="n">
-        <v>2253</v>
+        <v>2314</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -827,12 +827,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:06.433264</t>
+          <t>2026-06-27 01:41:55.712364</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>4화
 별점
-9.60
+9.59
 25.06.09</t>
         </is>
       </c>
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="K6" t="n">
-        <v>1932</v>
+        <v>1988</v>
       </c>
       <c r="L6" t="n">
-        <v>1916</v>
+        <v>1972</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:12.569965</t>
+          <t>2026-06-27 01:42:02.381981</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>5화
 별점
-9.66
+9.65
 25.06.16</t>
         </is>
       </c>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="K7" t="n">
-        <v>1804</v>
+        <v>1862</v>
       </c>
       <c r="L7" t="n">
-        <v>1736</v>
+        <v>1792</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -993,12 +993,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:17.184778</t>
+          <t>2026-06-27 01:42:07.644709</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>6화
 별점
-9.75
+9.73
 25.06.23</t>
         </is>
       </c>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="K8" t="n">
-        <v>1687</v>
+        <v>1739</v>
       </c>
       <c r="L8" t="n">
-        <v>1570</v>
+        <v>1618</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:21.687218</t>
+          <t>2026-06-27 01:42:13.829749</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1090,13 +1090,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>7화
 별점
-9.80
+9.81
 25.06.30</t>
         </is>
       </c>
@@ -1147,10 +1147,10 @@
         <v>9.81</v>
       </c>
       <c r="K9" t="n">
-        <v>1630</v>
+        <v>1682</v>
       </c>
       <c r="L9" t="n">
-        <v>1545</v>
+        <v>1595</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:26.255094</t>
+          <t>2026-06-27 01:42:19.731617</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1230,10 +1230,10 @@
         <v>9.85</v>
       </c>
       <c r="K10" t="n">
-        <v>1526</v>
+        <v>1579</v>
       </c>
       <c r="L10" t="n">
-        <v>1444</v>
+        <v>1492</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:30.917148</t>
+          <t>2026-06-27 01:42:25.263745</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>1532</v>
+        <v>1584</v>
       </c>
       <c r="L11" t="n">
-        <v>1347</v>
+        <v>1393</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:35.321624</t>
+          <t>2026-06-27 01:42:31.267467</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>10화
 별점
-9.79
+9.80
 25.07.21</t>
         </is>
       </c>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="K12" t="n">
-        <v>1532</v>
+        <v>1588</v>
       </c>
       <c r="L12" t="n">
-        <v>1330</v>
+        <v>1378</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:39.588726</t>
+          <t>2026-06-27 01:42:37.318427</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1422,13 +1422,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>11화
 별점
-9.86
+9.85
 25.07.28</t>
         </is>
       </c>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1438</v>
+        <v>1494</v>
       </c>
       <c r="L13" t="n">
-        <v>1292</v>
+        <v>1343</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:44.505152</t>
+          <t>2026-06-27 01:42:42.517644</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>12화
 별점
-9.87
+9.88
 25.08.04</t>
         </is>
       </c>
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1415</v>
+        <v>1468</v>
       </c>
       <c r="L14" t="n">
-        <v>1230</v>
+        <v>1276</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:48.653325</t>
+          <t>2026-06-27 01:42:47.783959</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>13화
 별점
-9.71
+9.72
 25.08.11</t>
         </is>
       </c>
@@ -1645,10 +1645,10 @@
         <v>9.880000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>1401</v>
+        <v>1459</v>
       </c>
       <c r="L15" t="n">
-        <v>1255</v>
+        <v>1308</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:53.006899</t>
+          <t>2026-06-27 01:42:53.269908</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1728,10 +1728,10 @@
         <v>9.710000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1362</v>
+        <v>1423</v>
       </c>
       <c r="L16" t="n">
-        <v>1234</v>
+        <v>1288</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:44.502682</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-06-05 03:12:57.940671</t>
+          <t>2026-06-27 01:42:58.952624</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="K17" t="n">
-        <v>1312</v>
+        <v>1369</v>
       </c>
       <c r="L17" t="n">
-        <v>1148</v>
+        <v>1196</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:02.673985</t>
+          <t>2026-06-27 01:43:04.670319</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>16화
 별점
-9.86
+9.85
 25.09.01</t>
         </is>
       </c>
@@ -1894,10 +1894,10 @@
         <v>9.880000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1267</v>
+        <v>1318</v>
       </c>
       <c r="L18" t="n">
-        <v>1144</v>
+        <v>1197</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:06.503643</t>
+          <t>2026-06-27 01:43:09.737783</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1977,10 +1977,10 @@
         <v>9.81</v>
       </c>
       <c r="K19" t="n">
-        <v>1253</v>
+        <v>1303</v>
       </c>
       <c r="L19" t="n">
-        <v>1108</v>
+        <v>1158</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:28.508364</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:11.241232</t>
+          <t>2026-06-27 01:43:15.699130</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>1197</v>
+        <v>1250</v>
       </c>
       <c r="L20" t="n">
-        <v>1098</v>
+        <v>1143</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:15.292054</t>
+          <t>2026-06-27 01:43:21.087928</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>19화
 별점
-9.77
+9.78
 25.09.22</t>
         </is>
       </c>
@@ -2143,10 +2143,10 @@
         <v>9.859999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>1192</v>
+        <v>1245</v>
       </c>
       <c r="L21" t="n">
-        <v>1077</v>
+        <v>1126</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:20.323889</t>
+          <t>2026-06-27 01:43:26.822963</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="K22" t="n">
-        <v>1182</v>
+        <v>1237</v>
       </c>
       <c r="L22" t="n">
-        <v>962</v>
+        <v>1011</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:24.959251</t>
+          <t>2026-06-27 01:43:32.457301</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>21화
 별점
-9.04
+9.08
 25.10.06</t>
         </is>
       </c>
@@ -2309,10 +2309,10 @@
         <v>9.539999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>1141</v>
+        <v>1198</v>
       </c>
       <c r="L23" t="n">
-        <v>955</v>
+        <v>1007</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:29.041433</t>
+          <t>2026-06-27 01:43:37.189705</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="K24" t="n">
-        <v>1072</v>
+        <v>1126</v>
       </c>
       <c r="L24" t="n">
-        <v>1003</v>
+        <v>1047</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:38.176737</t>
+          <t>2026-06-27 01:43:41.841941</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>23화
 별점
-9.82
+9.83
 25.10.20</t>
         </is>
       </c>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>1039</v>
+        <v>1092</v>
       </c>
       <c r="L25" t="n">
-        <v>922</v>
+        <v>975</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:41.943185</t>
+          <t>2026-06-27 01:43:46.392382</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>24화
 별점
-9.86
+9.87
 25.10.27</t>
         </is>
       </c>
@@ -2558,10 +2558,10 @@
         <v>9.83</v>
       </c>
       <c r="K26" t="n">
-        <v>1003</v>
+        <v>1056</v>
       </c>
       <c r="L26" t="n">
-        <v>913</v>
+        <v>959</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:45.591263</t>
+          <t>2026-06-27 01:43:51.175900</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>994</v>
+        <v>1043</v>
       </c>
       <c r="L27" t="n">
-        <v>876</v>
+        <v>925</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:50.610821</t>
+          <t>2026-06-27 01:43:55.592164</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>26화
 별점
-9.78
+9.79
 25.11.10</t>
         </is>
       </c>
@@ -2724,10 +2724,10 @@
         <v>9.92</v>
       </c>
       <c r="K28" t="n">
-        <v>1072</v>
+        <v>1127</v>
       </c>
       <c r="L28" t="n">
-        <v>940</v>
+        <v>987</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:55.424801</t>
+          <t>2026-06-27 01:44:00.575515</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="K29" t="n">
-        <v>1019</v>
+        <v>1070</v>
       </c>
       <c r="L29" t="n">
-        <v>911</v>
+        <v>956</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-06-05 03:13:59.927641</t>
+          <t>2026-06-27 01:44:05.077455</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>28화
 별점
-9.81
+9.82
 25.11.24</t>
         </is>
       </c>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>1002</v>
+        <v>1057</v>
       </c>
       <c r="L30" t="n">
-        <v>864</v>
+        <v>909</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:03.710576</t>
+          <t>2026-06-27 01:44:09.743998</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>29화
 별점
-9.85
+9.86
 25.12.01</t>
         </is>
       </c>
@@ -2970,13 +2970,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>971</v>
+        <v>1027</v>
       </c>
       <c r="L31" t="n">
-        <v>850</v>
+        <v>894</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:07.930614</t>
+          <t>2026-06-27 01:44:14.162401</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>30화
 별점
-9.87
+9.88
 25.12.08</t>
         </is>
       </c>
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>923</v>
+        <v>975</v>
       </c>
       <c r="L32" t="n">
-        <v>812</v>
+        <v>857</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:12.963085</t>
+          <t>2026-06-27 01:44:18.676755</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>31화
 별점
-9.85
+9.86
 25.12.15</t>
         </is>
       </c>
@@ -3139,10 +3139,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>952</v>
+        <v>1008</v>
       </c>
       <c r="L33" t="n">
-        <v>798</v>
+        <v>844</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:17.195538</t>
+          <t>2026-06-27 01:44:23.429496</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3219,13 +3219,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
       <c r="K34" t="n">
-        <v>932</v>
+        <v>987</v>
       </c>
       <c r="L34" t="n">
-        <v>779</v>
+        <v>825</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:21.647729</t>
+          <t>2026-06-27 01:44:27.994807</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>33화
 별점
-9.76
+9.77
 25.12.29</t>
         </is>
       </c>
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>9.640000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="K35" t="n">
-        <v>1207</v>
+        <v>1268</v>
       </c>
       <c r="L35" t="n">
-        <v>755</v>
+        <v>805</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:25.693907</t>
+          <t>2026-06-27 01:44:32.412036</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3331,13 +3331,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>9.640000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>34화
 별점
-9.64
+9.66
 26.01.05</t>
         </is>
       </c>
@@ -3385,13 +3385,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="K36" t="n">
-        <v>913</v>
+        <v>970</v>
       </c>
       <c r="L36" t="n">
-        <v>759</v>
+        <v>808</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:43.734104</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:29.749278</t>
+          <t>2026-06-27 01:44:37.213676</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3414,13 +3414,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>35화
 별점
-9.81
+9.82
 26.01.12</t>
         </is>
       </c>
@@ -3468,13 +3468,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="K37" t="n">
-        <v>880</v>
+        <v>936</v>
       </c>
       <c r="L37" t="n">
-        <v>733</v>
+        <v>781</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:33.664710</t>
+          <t>2026-06-27 01:44:42.530749</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>36화
 별점
-9.83
+9.84
 26.01.19</t>
         </is>
       </c>
@@ -3551,13 +3551,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>847</v>
+        <v>901</v>
       </c>
       <c r="L38" t="n">
-        <v>706</v>
+        <v>751</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:38.097171</t>
+          <t>2026-06-27 01:44:47.998784</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>37화
 별점
-9.79
+9.80
 26.01.26</t>
         </is>
       </c>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>9.35</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>895</v>
+        <v>949</v>
       </c>
       <c r="L39" t="n">
-        <v>660</v>
+        <v>706</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:27.735773</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:47.882674</t>
+          <t>2026-06-27 01:44:53.599001</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>9.35</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>38화
 별점
-9.35
+9.39
 26.02.02</t>
         </is>
       </c>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>867</v>
+        <v>926</v>
       </c>
       <c r="L40" t="n">
-        <v>706</v>
+        <v>754</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:53.599350</t>
+          <t>2026-06-27 01:44:58.415224</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>39화
 별점
-9.86
+9.87
 26.02.09</t>
         </is>
       </c>
@@ -3803,10 +3803,10 @@
         <v>9.9</v>
       </c>
       <c r="K41" t="n">
-        <v>797</v>
+        <v>855</v>
       </c>
       <c r="L41" t="n">
-        <v>672</v>
+        <v>723</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-06-05 03:14:58.028530</t>
+          <t>2026-06-27 01:45:03.566479</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>9.720000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="K42" t="n">
-        <v>769</v>
+        <v>825</v>
       </c>
       <c r="L42" t="n">
-        <v>628</v>
+        <v>676</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:02.799600</t>
+          <t>2026-06-27 01:45:09.034027</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3912,13 +3912,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>9.720000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>41화
 별점
-9.72
+9.74
 26.02.23</t>
         </is>
       </c>
@@ -3966,13 +3966,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="K43" t="n">
-        <v>784</v>
+        <v>847</v>
       </c>
       <c r="L43" t="n">
-        <v>628</v>
+        <v>678</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:07.685238</t>
+          <t>2026-06-27 01:45:14.084119</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3995,13 +3995,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>42화
 별점
-9.73
+9.74
 26.03.02</t>
         </is>
       </c>
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>800</v>
+        <v>860</v>
       </c>
       <c r="L44" t="n">
-        <v>625</v>
+        <v>678</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:12.515678</t>
+          <t>2026-06-27 01:45:19.283781</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4078,13 +4078,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>43화
 별점
-9.78
+9.80
 26.03.09</t>
         </is>
       </c>
@@ -4132,13 +4132,13 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="K45" t="n">
-        <v>741</v>
+        <v>805</v>
       </c>
       <c r="L45" t="n">
-        <v>572</v>
+        <v>626</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:17.350509</t>
+          <t>2026-06-27 01:45:24.750621</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4161,13 +4161,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
           <t>44화
 별점
-9.81
+9.82
 26.03.16</t>
         </is>
       </c>
@@ -4215,13 +4215,13 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>9.6</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>734</v>
+        <v>803</v>
       </c>
       <c r="L46" t="n">
-        <v>551</v>
+        <v>600</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:21.919360</t>
+          <t>2026-06-27 01:45:29.586091</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4244,13 +4244,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>9.6</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>45화
 별점
-9.60
+9.61
 26.03.23</t>
         </is>
       </c>
@@ -4298,13 +4298,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="K47" t="n">
-        <v>713</v>
+        <v>783</v>
       </c>
       <c r="L47" t="n">
-        <v>549</v>
+        <v>603</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:26.438040</t>
+          <t>2026-06-27 01:45:35.320208</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>46화
 별점
-9.83
+9.84
 26.03.30</t>
         </is>
       </c>
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>9.81</v>
+        <v>9.83</v>
       </c>
       <c r="K48" t="n">
-        <v>648</v>
+        <v>712</v>
       </c>
       <c r="L48" t="n">
-        <v>546</v>
+        <v>605</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:30.287090</t>
+          <t>2026-06-27 01:45:40.537785</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>9.81</v>
+        <v>9.83</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
           <t>47화
 별점
-9.81
+9.83
 26.04.06</t>
         </is>
       </c>
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="K49" t="n">
-        <v>677</v>
+        <v>748</v>
       </c>
       <c r="L49" t="n">
-        <v>533</v>
+        <v>594</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:34.533967</t>
+          <t>2026-06-27 01:45:46.071656</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4493,13 +4493,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>48화
 별점
-9.83
+9.85
 26.04.13</t>
         </is>
       </c>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="K50" t="n">
-        <v>676</v>
+        <v>749</v>
       </c>
       <c r="L50" t="n">
-        <v>504</v>
+        <v>562</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4562,12 +4562,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:38.770188</t>
+          <t>2026-06-27 01:45:51.253774</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4576,13 +4576,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>49화
 별점
-9.83
+9.84
 26.04.20</t>
         </is>
       </c>
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>9.59</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>667</v>
+        <v>743</v>
       </c>
       <c r="L51" t="n">
-        <v>483</v>
+        <v>545</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:42.770016</t>
+          <t>2026-06-27 01:45:57.053314</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4659,13 +4659,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>9.59</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>50화
 별점
-9.59
+9.63
 26.04.27</t>
         </is>
       </c>
@@ -4713,13 +4713,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>9.76</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>638</v>
+        <v>713</v>
       </c>
       <c r="L52" t="n">
-        <v>480</v>
+        <v>551</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:47.289198</t>
+          <t>2026-06-27 01:46:02.621053</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4742,13 +4742,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>9.76</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
           <t>51화
 별점
-9.76
+9.78
 26.05.04</t>
         </is>
       </c>
@@ -4796,13 +4796,13 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="K53" t="n">
-        <v>592</v>
+        <v>672</v>
       </c>
       <c r="L53" t="n">
-        <v>445</v>
+        <v>524</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:52.374238</t>
+          <t>2026-06-27 01:46:08.673609</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4825,13 +4825,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>52화
 별점
-9.83
+9.85
 26.05.11</t>
         </is>
       </c>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>548</v>
+        <v>645</v>
       </c>
       <c r="L54" t="n">
-        <v>438</v>
+        <v>517</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-06-05 03:15:56.438722</t>
+          <t>2026-06-27 01:46:14.305748</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4908,13 +4908,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>53화
 별점
-9.88
+9.89
 26.05.18</t>
         </is>
       </c>
@@ -4962,13 +4962,13 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>9.77</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>513</v>
+        <v>619</v>
       </c>
       <c r="L55" t="n">
-        <v>399</v>
+        <v>497</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4977,12 +4977,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-06-05 03:16:00.208305</t>
+          <t>2026-06-27 01:46:20.155589</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4991,13 +4991,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>9.77</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
           <t>54화
 별점
-9.77
+9.80
 26.05.25</t>
         </is>
       </c>
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="K56" t="n">
-        <v>483</v>
+        <v>656</v>
       </c>
       <c r="L56" t="n">
-        <v>333</v>
+        <v>476</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-06-05 03:11:42.969059</t>
+          <t>2026-06-27 01:41:26.967644</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-06-05 03:16:05.172111</t>
+          <t>2026-06-27 01:46:25.808625</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5074,14 +5074,180 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
           <t>55화
 별점
-9.82
+9.84
 26.06.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>839353</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>한계 찢는 천재마법사</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>56</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>56화</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>26.06.08</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:00:00</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="K57" t="n">
+        <v>583</v>
+      </c>
+      <c r="L57" t="n">
+        <v>446</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/detail?titleId=839353&amp;no=56&amp;week=tue</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:41:26.967644</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:46:30.443043</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>56화</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>56화
+별점
+9.83
+26.06.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>839353</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>한계 찢는 천재마법사</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>57</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>57화</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>26.06.15</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-06-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:00:00</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>566</v>
+      </c>
+      <c r="L58" t="n">
+        <v>424</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/detail?titleId=839353&amp;no=57&amp;week=tue</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:41:26.967644</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:46:35.941977</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>57화</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>57화
+별점
+9.89
+26.06.15</t>
         </is>
       </c>
     </row>
